--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T09:14:32+00:00</t>
+    <t>2026-03-01T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,6 +94,10 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Description: Contains information protected by copyright of SNOMED International. Any use of SNOMED CT in Austria requires a valid affiliate license or sublicense. The corresponding license is free of charge, provided that the use only takes place in Austria and fulfills the conditions of the Affiliate License Agreement. Affiliate licenses can be requested directly from the respective NRC via the Member Licensing and Distribution Service (MLDS).https://wiki.hl7.at/index.php?title=SCT:SNOMED_CT
+Beschreibung: Enthält durch SNOMED International urheberrechtlich geschützte Information. Jede Verwendung von SNOMED CT in Österreich erfordert eine aufrechte Affiliate Lizenz oder eine Sublizenz. Die entsprechende Lizenz ist kostenlos, vorausgesetzt die Verwendung findet nur in Österreich statt und erfüllt die Bedingungen des Affiliate License Agreements. Affiliate Lizenzen können über das Member Licensing and Distribution Service (MLDS) direkt beim jeweiligen NRC beantragt werden.https://wiki.hl7.at/index.php?title=SCT:SNOMED_CT</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -417,14 +421,16 @@
       <c r="A15" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -443,7 +449,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>23</v>
@@ -451,74 +457,74 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -531,10 +537,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>SNOMED CT AlcoholUse-Frequency</t>
+    <t>AT PreNUDGE Alcohol Use Frequency</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet containing SNOMED CT codes for differentiating frequencies used in the PreNUDGE alcoholuse questionnaire.</t>
+    <t>Frequencies used in the PreNUDGE alcoholuse questionnaire.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-alcoholuse-frequency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
